--- a/artfynd/A 35023-2024 artfynd.xlsx
+++ b/artfynd/A 35023-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119442085</v>
+        <v>119442096</v>
       </c>
       <c r="B2" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>464778</v>
+        <v>464659</v>
       </c>
       <c r="R2" t="n">
-        <v>7080548</v>
+        <v>7080373</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-08-29</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119442101</v>
+        <v>119442111</v>
       </c>
       <c r="B3" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>464823</v>
+        <v>464743</v>
       </c>
       <c r="R3" t="n">
-        <v>7080583</v>
+        <v>7080171</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,37 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119442102</v>
+        <v>119442112</v>
       </c>
       <c r="B4" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>464809</v>
+        <v>464723</v>
       </c>
       <c r="R4" t="n">
-        <v>7080201</v>
+        <v>7080367</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +945,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,19 +976,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119442114</v>
+        <v>119442113</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1026,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464778</v>
+        <v>464747</v>
       </c>
       <c r="R5" t="n">
-        <v>7080550</v>
+        <v>7080510</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,37 +1078,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119442103</v>
+        <v>119442114</v>
       </c>
       <c r="B6" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465067</v>
+        <v>464778</v>
       </c>
       <c r="R6" t="n">
-        <v>7080449</v>
+        <v>7080550</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,6 +1149,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,37 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119442084</v>
+        <v>119442115</v>
       </c>
       <c r="B7" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464820</v>
+        <v>465016</v>
       </c>
       <c r="R7" t="n">
-        <v>7080600</v>
+        <v>7080486</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,11 +1251,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-08-29</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,15 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119442113</v>
+        <v>119442084</v>
       </c>
       <c r="B8" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1318,21 +1288,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464747</v>
+        <v>464820</v>
       </c>
       <c r="R8" t="n">
-        <v>7080510</v>
+        <v>7080600</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,7 +1352,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,15 +1379,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119442115</v>
+        <v>119442085</v>
       </c>
       <c r="B9" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1425,21 +1390,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1414,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465016</v>
+        <v>464778</v>
       </c>
       <c r="R9" t="n">
-        <v>7080486</v>
+        <v>7080548</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1487,6 +1452,11 @@
           <t>2024-08-29</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1508,322 +1478,6 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>119442111</v>
-      </c>
-      <c r="B10" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Djupvattsbodarna, Jmt</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>464743</v>
-      </c>
-      <c r="R10" t="n">
-        <v>7080171</v>
-      </c>
-      <c r="S10" t="n">
-        <v>10</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2024-08-29</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2024-08-29</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>119442112</v>
-      </c>
-      <c r="B11" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Djupvattsbodarna, Jmt</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>464723</v>
-      </c>
-      <c r="R11" t="n">
-        <v>7080367</v>
-      </c>
-      <c r="S11" t="n">
-        <v>10</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2024-08-29</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2024-08-29</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>119442096</v>
-      </c>
-      <c r="B12" t="n">
-        <v>90558</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>1108</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Harticka</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Djupvattsbodarna, Jmt</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>464659</v>
-      </c>
-      <c r="R12" t="n">
-        <v>7080373</v>
-      </c>
-      <c r="S12" t="n">
-        <v>10</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2024-08-29</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2024-08-29</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35023-2024 artfynd.xlsx
+++ b/artfynd/A 35023-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119442096</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119442111</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119442112</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,6 +1095,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119442113</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119442114</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1274,6 +1304,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119442115</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1376,6 +1411,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119442084</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1478,8 +1518,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119442085</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>